--- a/Statement_Mapping.xlsx
+++ b/Statement_Mapping.xlsx
@@ -9274,7 +9274,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Motor vehicles</t>
+          <t>Spare parts and labour</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Motor Vehicles Sales</t>
+          <t>Spare Parts &amp; After-Sales</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr"/>
